--- a/sample-imports/instruments/instruments_sample.xlsx
+++ b/sample-imports/instruments/instruments_sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SN-2026-001</t>
+          <t>SN-2026-101</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AN-1001</t>
+          <t>AN-2101</t>
         </is>
       </c>
     </row>
@@ -518,12 +518,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SN-2026-002</t>
+          <t>SN-2026-102</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AN-1002</t>
+          <t>AN-2102</t>
         </is>
       </c>
     </row>
@@ -555,12 +555,456 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SN-2026-003</t>
+          <t>SN-2026-103</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AN-1003</t>
+          <t>AN-2103</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HPLC System</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chromatograph</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Agilent Technologies</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Scientific Traders Co</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1260 Infinity II</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SN-2026-104</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AN-2104</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Gas Chromatograph</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Chromatograph</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PerkinElmer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LabTech Supplies</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Clarus 590</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SN-2026-105</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AN-2105</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Centrifuge</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Centrifuge</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Eppendorf</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Precision Instruments Ltd</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5810 R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SN-2026-106</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AN-2106</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Autoclave</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sterilizer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tuttnauer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ChemLab Traders</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3870EL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SN-2026-107</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AN-2107</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Incubator</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Incubator</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Scientific Traders Co</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Heratherm IGS180</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SN-2026-108</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AN-2108</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Water Bath</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Water Bath</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Julabo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LabTech Supplies</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TW20</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SN-2026-109</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AN-2109</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Muffle Furnace</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Furnace</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Carbolite Gero</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Precision Instruments Ltd</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CWF 1300</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SN-2026-110</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AN-2110</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Refractometer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Refractometer</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Anton Paar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ChemLab Traders</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Abbemat 200</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SN-2026-111</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AN-2111</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Karl Fischer Titrator</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Titrator</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Metrohm</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Scientific Traders Co</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>870 KF</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SN-2026-112</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>AN-2112</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Moisture Analyzer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Moisture Analyzer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sartorius</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LabTech Supplies</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MA37</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SN-2026-113</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AN-2113</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dissolution Tester</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dissolution Tester</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Agilent Technologies</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Precision Instruments Ltd</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>708-DS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SN-2026-114</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AN-2114</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Microscope</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Microscope</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Olympus</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ChemLab Traders</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CX23</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SN-2026-115</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AN-2115</t>
         </is>
       </c>
     </row>
